--- a/010_NASA_GlennIce/gridConvergence_D01_V1.xlsx
+++ b/010_NASA_GlennIce/gridConvergence_D01_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkzayni/Desktop/UNIVERSITY/POST_PROCESS/postProcessingData/010_NASA_GlennIce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taozoros/Documents/IPW3/GLENNICE-RESULT/010_IPW3-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5731488-2DF1-2245-819F-10A436C1D6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1730F634-C6B3-324F-8501-AE3F8852B04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44160" yWindow="-9380" windowWidth="34560" windowHeight="20040" tabRatio="500" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -440,13 +440,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.0000E+00"/>
     <numFmt numFmtId="167" formatCode="0.00000E+00"/>
+    <numFmt numFmtId="168" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -512,10 +513,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Menlo"/>
-      <family val="2"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="5">
@@ -669,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -785,27 +791,37 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -820,33 +836,6 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -856,10 +845,52 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1274,23 +1305,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="55"/>
+      <c r="A2" s="46"/>
     </row>
     <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="55"/>
+      <c r="A3" s="46"/>
     </row>
     <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="46" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="55"/>
+      <c r="A5" s="46"/>
     </row>
     <row r="6" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1328,12 +1359,12 @@
       </c>
     </row>
     <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="47" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="56"/>
+      <c r="A14" s="47"/>
     </row>
     <row r="15" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1361,12 +1392,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="46" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="55"/>
+      <c r="A21" s="46"/>
     </row>
     <row r="22" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
@@ -1422,13 +1453,13 @@
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="55" t="s">
+      <c r="A32" s="46" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="55"/>
+      <c r="A33" s="46"/>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1491,12 +1522,12 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="55" t="s">
+      <c r="A44" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="55"/>
+      <c r="A45" s="46"/>
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1560,12 +1591,12 @@
       <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="55" t="s">
+      <c r="A56" s="46" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="55"/>
+      <c r="A57" s="46"/>
       <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1684,65 +1715,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
     </row>
     <row r="2" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="49"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="61"/>
     </row>
     <row r="3" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="53"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="55"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
@@ -1998,9 +2029,15 @@
       <c r="A12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="11">
+        <v>3.80160407042733</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1.28872728279731</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.50029029784183099</v>
+      </c>
       <c r="E12" s="20"/>
       <c r="F12" s="20" t="s">
         <v>59</v>
@@ -2030,46 +2067,46 @@
       <c r="O12" s="20"/>
     </row>
     <row r="13" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="49"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="61"/>
     </row>
     <row r="14" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50" t="s">
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="51" t="s">
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="53"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="55"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="20" t="s">
@@ -2363,46 +2400,46 @@
       <c r="O23" s="20"/>
     </row>
     <row r="24" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="49"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="61"/>
     </row>
     <row r="25" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50" t="s">
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="51" t="s">
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="L25" s="52"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="52"/>
-      <c r="O25" s="53"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="55"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="20" t="s">
@@ -2696,46 +2733,46 @@
       <c r="O34" s="20"/>
     </row>
     <row r="35" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A35" s="47" t="s">
+      <c r="A35" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="49"/>
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="60"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="61"/>
     </row>
     <row r="36" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50" t="s">
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="51" t="s">
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="53"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="54"/>
+      <c r="O36" s="55"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
@@ -3064,12 +3101,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
     </row>
     <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -4124,12 +4161,12 @@
       <c r="AMJ3" s="10"/>
     </row>
     <row r="4" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -5198,12 +5235,12 @@
       <c r="AMJ6" s="10"/>
     </row>
     <row r="7" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -6272,12 +6309,12 @@
       <c r="AMJ9" s="10"/>
     </row>
     <row r="10" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -6312,7 +6349,7 @@
       <c r="A12" s="11">
         <v>0</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="43">
         <v>0.48566784499999999</v>
       </c>
       <c r="C12" s="11">
@@ -7352,12 +7389,12 @@
       <c r="R13" s="7"/>
     </row>
     <row r="14" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -7800,12 +7837,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="61"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="50"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
@@ -7928,12 +7965,12 @@
       <c r="O7" s="10"/>
     </row>
     <row r="8" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="I8" s="10"/>
@@ -8052,12 +8089,12 @@
       <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="61"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -8192,12 +8229,12 @@
       <c r="O21" s="10"/>
     </row>
     <row r="22" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="50"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="I22" s="10"/>
@@ -8338,12 +8375,12 @@
       <c r="O29" s="10"/>
     </row>
     <row r="30" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A30" s="62" t="s">
+      <c r="A30" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="62"/>
-      <c r="C30" s="62"/>
-      <c r="D30" s="62"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
@@ -8354,12 +8391,12 @@
       <c r="O30" s="10"/>
     </row>
     <row r="31" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
@@ -8806,7 +8843,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EA0DC49-B228-6142-89A2-F876D0182B62}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
@@ -8826,61 +8863,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="65"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="58"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="51" t="s">
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="52"/>
-      <c r="M3" s="53"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="55"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
@@ -8925,82 +8962,82 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="41">
         <v>0.116241207264764</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="41">
         <v>0.110777633195538</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="41">
         <v>5.4626811674013597E-3</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="41">
         <v>0.123465133490837</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="41">
         <v>0.115638389271103</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="41">
         <v>7.8260671415359799E-3</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="41">
         <v>0.124745458181565</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="41">
         <v>0.11609537664766199</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="41">
         <v>8.64949002762091E-3</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="41">
         <v>0.124752164135589</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="41">
         <v>0.11602111161661401</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="41">
         <v>8.7304716044790693E-3</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="49"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="61"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="51" t="s">
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="51" t="s">
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="52"/>
-      <c r="M7" s="53"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="55"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="18"/>
@@ -9045,82 +9082,82 @@
       <c r="A9" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="41">
         <v>0.116254955561508</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="41">
         <v>0.110721798097403</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="41">
         <v>5.5323420134381204E-3</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="41">
         <v>0.12345770810954</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="41">
         <v>0.115588099394292</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="41">
         <v>7.8689868043219403E-3</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="41">
         <v>0.12474975756491199</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="41">
         <v>0.11605073137816201</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="41">
         <v>8.6984757046324208E-3</v>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="41">
         <v>0.124735747422462</v>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="41">
         <v>0.115948585148361</v>
       </c>
-      <c r="M9" s="42">
+      <c r="M9" s="41">
         <v>8.7866206976011298E-3</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51" t="s">
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="51" t="s">
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="52"/>
-      <c r="M11" s="53"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="55"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
@@ -9165,82 +9202,82 @@
       <c r="A13" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="42">
+      <c r="B13" s="41">
         <v>0.11608392163723701</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="41">
         <v>0.110544032681582</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="41">
         <v>5.5386394499039098E-3</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="41">
         <v>0.123312774080101</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="41">
         <v>0.11540413214662899</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="41">
         <v>7.9076656785333002E-3</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="41">
         <v>0.12465197645571401</v>
       </c>
-      <c r="I13" s="42">
+      <c r="I13" s="41">
         <v>0.115875673113781</v>
       </c>
-      <c r="J13" s="42">
+      <c r="J13" s="41">
         <v>8.7754266463720507E-3</v>
       </c>
-      <c r="K13" s="42">
+      <c r="K13" s="41">
         <v>0.12464580365033399</v>
       </c>
-      <c r="L13" s="42">
+      <c r="L13" s="41">
         <v>0.115793706024981</v>
       </c>
-      <c r="M13" s="42">
+      <c r="M13" s="41">
         <v>8.8512354494335293E-3</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51" t="s">
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="52"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="51" t="s">
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="52"/>
-      <c r="M15" s="53"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="55"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="18"/>
@@ -9285,48 +9322,45 @@
       <c r="A17" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="41">
         <v>0.11605313717378</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="41">
         <v>0.11046202313591</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="41">
         <v>5.59028139578659E-3</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="41">
         <v>0.12357452471534899</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="41">
         <v>0.115531270924979</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="41">
         <v>8.0426051264552607E-3</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="41">
         <v>0.124829476010112</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="41">
         <v>0.115970572505117</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="41">
         <v>8.8583224737415703E-3</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="41">
         <v>0.12482220192991</v>
       </c>
-      <c r="L17" s="42">
+      <c r="L17" s="41">
         <v>0.11589642809901</v>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="41">
         <v>8.9252032402091994E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="I19" s="42"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D22" s="42"/>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D26" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -9386,82 +9420,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
     </row>
     <row r="2" spans="1:25" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
     </row>
     <row r="3" spans="1:25" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50" t="s">
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
       <c r="V3" s="19"/>
       <c r="W3" s="19"/>
       <c r="X3" s="19"/>
@@ -9969,62 +10003,62 @@
       <c r="Y20" s="7"/>
     </row>
     <row r="21" spans="1:25" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="66"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
       <c r="U21" s="29"/>
       <c r="W21" s="30"/>
       <c r="X21" s="30"/>
       <c r="Y21" s="30"/>
     </row>
     <row r="22" spans="1:25" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50" t="s">
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50" t="s">
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50" t="s">
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="50"/>
-      <c r="T22" s="50"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
       <c r="W22" s="30"/>
       <c r="X22" s="30"/>
       <c r="Y22" s="30"/>
@@ -10518,61 +10552,61 @@
       <c r="Y39" s="7"/>
     </row>
     <row r="40" spans="1:25" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
-      <c r="N40" s="66"/>
-      <c r="O40" s="66"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="66"/>
-      <c r="S40" s="66"/>
-      <c r="T40" s="66"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="62"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="62"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="62"/>
       <c r="W40" s="30"/>
       <c r="X40" s="30"/>
       <c r="Y40" s="30"/>
     </row>
     <row r="41" spans="1:25" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="50" t="s">
+      <c r="A41" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50" t="s">
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50" t="s">
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50" t="s">
+      <c r="L41" s="52"/>
+      <c r="M41" s="52"/>
+      <c r="N41" s="52"/>
+      <c r="O41" s="52"/>
+      <c r="P41" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50"/>
-      <c r="S41" s="50"/>
-      <c r="T41" s="50"/>
+      <c r="Q41" s="52"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="52"/>
+      <c r="T41" s="52"/>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="20" t="s">
@@ -11012,58 +11046,58 @@
       <c r="T58" s="27"/>
     </row>
     <row r="59" spans="1:20" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A59" s="50" t="s">
+      <c r="A59" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="50"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="50"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="50"/>
-      <c r="H59" s="50"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
-      <c r="M59" s="50"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="50"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="52"/>
+      <c r="R59" s="52"/>
+      <c r="S59" s="52"/>
+      <c r="T59" s="52"/>
     </row>
     <row r="60" spans="1:20" s="28" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="50" t="s">
+      <c r="A60" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="50"/>
-      <c r="C60" s="50"/>
-      <c r="D60" s="50"/>
-      <c r="E60" s="50"/>
-      <c r="F60" s="50" t="s">
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G60" s="50"/>
-      <c r="H60" s="50"/>
-      <c r="I60" s="50"/>
-      <c r="J60" s="50"/>
-      <c r="K60" s="50" t="s">
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="52"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L60" s="50"/>
-      <c r="M60" s="50"/>
-      <c r="N60" s="50"/>
-      <c r="O60" s="50"/>
-      <c r="P60" s="50" t="s">
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52"/>
+      <c r="O60" s="52"/>
+      <c r="P60" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q60" s="50"/>
-      <c r="R60" s="50"/>
-      <c r="S60" s="50"/>
-      <c r="T60" s="50"/>
+      <c r="Q60" s="52"/>
+      <c r="R60" s="52"/>
+      <c r="S60" s="52"/>
+      <c r="T60" s="52"/>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" s="20" t="s">
@@ -11553,61 +11587,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="65"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="58"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="51" t="s">
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="52"/>
-      <c r="M3" s="53"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="55"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
@@ -11652,82 +11686,82 @@
       <c r="A5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="65">
         <v>0.116241207264764</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="74">
         <v>0.110728651206146</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="74">
         <v>5.5081984678383104E-3</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="65">
         <v>0.123465133490837</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="74">
         <v>0.114857613716097</v>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="74">
         <v>8.6047091408141194E-3</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="74">
         <v>0.124745458181565</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="74">
         <v>0.115156072165605</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="74">
         <v>9.5868174639248301E-3</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="74">
         <v>0.124752164135589</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="74">
         <v>0.115061956758177</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="74">
         <v>9.6876707805989993E-3</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="49"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="61"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="51" t="s">
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="51" t="s">
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="52"/>
-      <c r="M7" s="53"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="55"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="18"/>
@@ -11772,82 +11806,82 @@
       <c r="A9" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="65">
         <v>0.116254955561508</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="74">
         <v>0.11065030281926699</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="74">
         <v>5.60067292395408E-3</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="65">
         <v>0.12345770810954</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="65">
         <v>0.114802838904225</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="65">
         <v>8.6522508413729195E-3</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="65">
         <v>0.12474975756491199</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="65">
         <v>0.11509493901996599</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="65">
         <v>9.6524135254575805E-3</v>
       </c>
-      <c r="K9" s="44">
+      <c r="K9" s="73">
         <v>0.124735747422462</v>
       </c>
-      <c r="L9" s="44">
+      <c r="L9" s="73">
         <v>0.114974027401094</v>
       </c>
-      <c r="M9" s="44">
+      <c r="M9" s="73">
         <v>9.7593414833796396E-3</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51" t="s">
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="51" t="s">
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="52"/>
-      <c r="M11" s="53"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="55"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
@@ -11892,82 +11926,82 @@
       <c r="A13" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="72">
         <v>0.11608392163723701</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="68">
         <v>0.11043278401609299</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="68">
         <v>5.6461162321057197E-3</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="72">
         <v>0.123312774080101</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="68">
         <v>0.114598516295293</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="72">
         <v>8.7108071824058796E-3</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="68">
         <v>0.12465197645571401</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="69">
         <v>0.114886565136679</v>
       </c>
-      <c r="J13" s="45">
+      <c r="J13" s="69">
         <v>9.7622103021884205E-3</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="70">
         <v>0.12464580365033399</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="72">
         <v>0.114788825923233</v>
       </c>
-      <c r="M13" s="46">
+      <c r="M13" s="71">
         <v>9.8538143596354506E-3</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51" t="s">
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="52"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="51" t="s">
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="52"/>
-      <c r="M15" s="53"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="55"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="18"/>
@@ -12009,43 +12043,43 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="66">
         <v>0.11605313717378</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="66">
         <v>0.110340498868319</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="66">
         <v>5.7088067027975696E-3</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="66">
         <v>0.12357452471534899</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="66">
         <v>0.114688741555318</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="66">
         <v>8.8832338445563007E-3</v>
       </c>
-      <c r="H17" s="43">
+      <c r="H17" s="66">
         <v>0.124829476010112</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="66">
         <v>0.114959560637932</v>
       </c>
-      <c r="J17" s="43">
+      <c r="J17" s="66">
         <v>9.8675594453719907E-3</v>
       </c>
-      <c r="K17" s="43">
+      <c r="K17" s="66">
         <v>0.12482220192991</v>
       </c>
-      <c r="L17" s="43">
+      <c r="L17" s="66">
         <v>0.114868787889447</v>
       </c>
-      <c r="M17" s="43">
+      <c r="M17" s="66">
         <v>9.9510973020613108E-3</v>
       </c>
     </row>
@@ -12105,82 +12139,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
     </row>
     <row r="2" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
     </row>
     <row r="3" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50" t="s">
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
@@ -12707,58 +12741,58 @@
       <c r="T20" s="27"/>
     </row>
     <row r="21" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="66"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
     </row>
     <row r="22" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50" t="s">
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50" t="s">
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50" t="s">
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="50"/>
-      <c r="T22" s="50"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="20" t="s">
@@ -13285,58 +13319,58 @@
       <c r="T39" s="27"/>
     </row>
     <row r="40" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
-      <c r="N40" s="66"/>
-      <c r="O40" s="66"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="66"/>
-      <c r="S40" s="66"/>
-      <c r="T40" s="66"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="62"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="62"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="62"/>
     </row>
     <row r="41" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="50" t="s">
+      <c r="A41" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50" t="s">
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50" t="s">
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50" t="s">
+      <c r="L41" s="52"/>
+      <c r="M41" s="52"/>
+      <c r="N41" s="52"/>
+      <c r="O41" s="52"/>
+      <c r="P41" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50"/>
-      <c r="S41" s="50"/>
-      <c r="T41" s="50"/>
+      <c r="Q41" s="52"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="52"/>
+      <c r="T41" s="52"/>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="20" t="s">
@@ -13863,58 +13897,58 @@
       <c r="T58" s="27"/>
     </row>
     <row r="59" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A59" s="50" t="s">
+      <c r="A59" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="50"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="50"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="50"/>
-      <c r="H59" s="50"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
-      <c r="M59" s="50"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="50"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="52"/>
+      <c r="R59" s="52"/>
+      <c r="S59" s="52"/>
+      <c r="T59" s="52"/>
     </row>
     <row r="60" spans="1:20" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="50" t="s">
+      <c r="A60" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="50"/>
-      <c r="C60" s="50"/>
-      <c r="D60" s="50"/>
-      <c r="E60" s="50"/>
-      <c r="F60" s="50" t="s">
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G60" s="50"/>
-      <c r="H60" s="50"/>
-      <c r="I60" s="50"/>
-      <c r="J60" s="50"/>
-      <c r="K60" s="50" t="s">
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="52"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L60" s="50"/>
-      <c r="M60" s="50"/>
-      <c r="N60" s="50"/>
-      <c r="O60" s="50"/>
-      <c r="P60" s="50" t="s">
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52"/>
+      <c r="O60" s="52"/>
+      <c r="P60" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q60" s="50"/>
-      <c r="R60" s="50"/>
-      <c r="S60" s="50"/>
-      <c r="T60" s="50"/>
+      <c r="Q60" s="52"/>
+      <c r="R60" s="52"/>
+      <c r="S60" s="52"/>
+      <c r="T60" s="52"/>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" s="20" t="s">
@@ -14489,61 +14523,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="67"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="64"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="55"/>
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="51" t="s">
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="52"/>
-      <c r="M3" s="53"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="55"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="38"/>
@@ -14588,58 +14622,82 @@
       <c r="A5" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
+      <c r="B5" s="42">
+        <v>3.8105501230271401</v>
+      </c>
+      <c r="C5" s="42">
+        <v>1.66282129376999</v>
+      </c>
+      <c r="D5" s="42">
+        <v>0.58597375627715798</v>
+      </c>
+      <c r="E5" s="42">
+        <v>3.7828063732385901</v>
+      </c>
+      <c r="F5" s="42">
+        <v>1.69751636978217</v>
+      </c>
+      <c r="G5" s="42">
+        <v>0.63064104621112405</v>
+      </c>
+      <c r="H5" s="42">
+        <v>3.7695627152798501</v>
+      </c>
+      <c r="I5" s="42">
+        <v>1.6997604997340801</v>
+      </c>
+      <c r="J5" s="42">
+        <v>0.64921241240030403</v>
+      </c>
+      <c r="K5" s="42">
+        <v>3.7650305953044501</v>
+      </c>
+      <c r="L5" s="42">
+        <v>1.7026247902289</v>
+      </c>
+      <c r="M5" s="42">
+        <v>0.65270859349252097</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="55"/>
     </row>
     <row r="7" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="51" t="s">
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="51" t="s">
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="52"/>
-      <c r="M7" s="53"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="55"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="38"/>
@@ -14722,44 +14780,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="55"/>
     </row>
     <row r="11" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51" t="s">
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="51" t="s">
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="52"/>
-      <c r="M11" s="53"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="55"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="38"/>
@@ -14842,44 +14900,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="55"/>
     </row>
     <row r="15" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51" t="s">
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="52"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="51" t="s">
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="52"/>
-      <c r="M15" s="53"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="55"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="38"/>
@@ -15019,23 +15077,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
       <c r="U1" s="32"/>
       <c r="V1" s="32"/>
       <c r="W1" s="32"/>
@@ -16047,28 +16105,28 @@
       <c r="AMO1" s="32"/>
     </row>
     <row r="2" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
       <c r="U2" s="32"/>
       <c r="V2" s="32"/>
       <c r="W2" s="32"/>
@@ -17080,34 +17138,34 @@
       <c r="AMO2" s="32"/>
     </row>
     <row r="3" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="50" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50" t="s">
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
       <c r="U3" s="32"/>
       <c r="V3" s="32"/>
       <c r="W3" s="22"/>
@@ -18466,28 +18524,28 @@
       <c r="V20" s="15"/>
     </row>
     <row r="21" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="52"/>
+      <c r="P21" s="52"/>
+      <c r="Q21" s="52"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="52"/>
+      <c r="T21" s="52"/>
       <c r="U21" s="34"/>
       <c r="V21" s="34"/>
       <c r="W21" s="32"/>
@@ -19499,34 +19557,34 @@
       <c r="AMO21" s="32"/>
     </row>
     <row r="22" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="50" t="s">
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50" t="s">
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50" t="s">
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="50"/>
-      <c r="T22" s="50"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
       <c r="U22" s="32"/>
       <c r="V22" s="32"/>
       <c r="W22" s="32"/>
@@ -20887,28 +20945,28 @@
       <c r="T39" s="25"/>
     </row>
     <row r="40" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
-      <c r="N40" s="66"/>
-      <c r="O40" s="66"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="66"/>
-      <c r="S40" s="66"/>
-      <c r="T40" s="66"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="62"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="62"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="62"/>
       <c r="U40" s="32"/>
       <c r="V40" s="32"/>
       <c r="W40" s="32"/>
@@ -21920,34 +21978,34 @@
       <c r="AMO40" s="32"/>
     </row>
     <row r="41" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="50" t="s">
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50" t="s">
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50" t="s">
+      <c r="L41" s="52"/>
+      <c r="M41" s="52"/>
+      <c r="N41" s="52"/>
+      <c r="O41" s="52"/>
+      <c r="P41" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50"/>
-      <c r="S41" s="50"/>
-      <c r="T41" s="50"/>
+      <c r="Q41" s="52"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="52"/>
+      <c r="T41" s="52"/>
       <c r="U41" s="32"/>
       <c r="V41" s="32"/>
       <c r="W41" s="32"/>
@@ -23308,28 +23366,28 @@
       <c r="T58" s="25"/>
     </row>
     <row r="59" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A59" s="66" t="s">
+      <c r="A59" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="66"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="66"/>
-      <c r="J59" s="66"/>
-      <c r="K59" s="66"/>
-      <c r="L59" s="66"/>
-      <c r="M59" s="66"/>
-      <c r="N59" s="66"/>
-      <c r="O59" s="66"/>
-      <c r="P59" s="66"/>
-      <c r="Q59" s="66"/>
-      <c r="R59" s="66"/>
-      <c r="S59" s="66"/>
-      <c r="T59" s="66"/>
+      <c r="B59" s="62"/>
+      <c r="C59" s="62"/>
+      <c r="D59" s="62"/>
+      <c r="E59" s="62"/>
+      <c r="F59" s="62"/>
+      <c r="G59" s="62"/>
+      <c r="H59" s="62"/>
+      <c r="I59" s="62"/>
+      <c r="J59" s="62"/>
+      <c r="K59" s="62"/>
+      <c r="L59" s="62"/>
+      <c r="M59" s="62"/>
+      <c r="N59" s="62"/>
+      <c r="O59" s="62"/>
+      <c r="P59" s="62"/>
+      <c r="Q59" s="62"/>
+      <c r="R59" s="62"/>
+      <c r="S59" s="62"/>
+      <c r="T59" s="62"/>
       <c r="U59" s="32"/>
       <c r="V59" s="32"/>
       <c r="W59" s="32"/>
@@ -24341,34 +24399,34 @@
       <c r="AMO59" s="32"/>
     </row>
     <row r="60" spans="1:1029" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A60" s="51" t="s">
+      <c r="A60" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="52"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="52"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="50" t="s">
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G60" s="50"/>
-      <c r="H60" s="50"/>
-      <c r="I60" s="50"/>
-      <c r="J60" s="50"/>
-      <c r="K60" s="50" t="s">
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="52"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="L60" s="50"/>
-      <c r="M60" s="50"/>
-      <c r="N60" s="50"/>
-      <c r="O60" s="50"/>
-      <c r="P60" s="50" t="s">
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52"/>
+      <c r="O60" s="52"/>
+      <c r="P60" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Q60" s="50"/>
-      <c r="R60" s="50"/>
-      <c r="S60" s="50"/>
-      <c r="T60" s="50"/>
+      <c r="Q60" s="52"/>
+      <c r="R60" s="52"/>
+      <c r="S60" s="52"/>
+      <c r="T60" s="52"/>
       <c r="U60" s="32"/>
       <c r="V60" s="32"/>
       <c r="W60" s="32"/>
